--- a/data/merged/2026-08-31/MERGED_US_Robot-Vacuum_2026-08-31.xlsx
+++ b/data/merged/2026-08-31/MERGED_US_Robot-Vacuum_2026-08-31.xlsx
@@ -7330,94 +7330,6 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>49</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>49</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="49" name="Product 49">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <ns2:creationId id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId49" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="50" name="Product 50">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <ns2:creationId id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId50" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -7743,7 +7655,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:BR51"/>
+  <dimension ref="A1:BR49"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="5" style="1" customWidth="1"/>
@@ -18031,125 +17943,115 @@
       <c r="B44" s="13"/>
       <c r="C44" s="14" t="inlineStr">
         <is>
-          <t>B0C7C7PLLG</t>
+          <t>B0GZPM94M2</t>
         </is>
       </c>
       <c r="D44" s="14"/>
       <c r="E44" s="14"/>
       <c r="F44" s="14" t="inlineStr">
         <is>
-          <t>eufy</t>
+          <t>Redroad</t>
         </is>
       </c>
       <c r="G44" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/stores/eufy/page/B02CB877-324C-4130-B1A3-41E418F2C467?lp_asin=B0C7C7PLLG&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.com/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Redroad</t>
         </is>
       </c>
       <c r="H44" s="14" t="inlineStr">
         <is>
-          <t>eufy RoboVac Hard Floor Cleaning Solution (2 Bottles), Dilution Ratio 1:200, 473 ml, Floor Cleaner, Plant-Based,Compatible wi</t>
+          <t>Redroad Robot Vacuum 20,000Pa Robot Vacuum Mop,120Day Self Emptying Vacuum Robot,Lidar Navigation,2.4G 5G WiFi APP Aspirateur</t>
         </is>
       </c>
       <c r="I44" s="14"/>
       <c r="J44" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/dp/B0C7C7PLLG?psc=1</t>
+          <t>https://www.amazon.com/dp/B0GZPM94M2?psc=1</t>
         </is>
       </c>
       <c r="K44" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/511jqutQR2L._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/71GaguO8jGL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L44" s="14" t="inlineStr">
         <is>
-          <t>B0C7C7PLLG</t>
+          <t>B0GZPM94M2</t>
         </is>
       </c>
       <c r="M44" s="14" t="inlineStr">
         <is>
-          <t>Industrial &amp; Scientific:Janitorial &amp; Sanitation Supplies:Vacuums &amp; Floor Cleaning Machines:Vacuums:Robotic Vacuums</t>
+          <t>Home &amp; Kitchen:Vacuums &amp; Floor Care:Vacuums:Robotic Vacuums</t>
         </is>
       </c>
       <c r="N44" s="14" t="inlineStr">
         <is>
-          <t>Industrial &amp; Scientific</t>
+          <t>Home &amp; Kitchen</t>
         </is>
       </c>
       <c r="O44" s="15">
-        <v>2305</v>
+        <v>31155</v>
       </c>
       <c r="P44" s="15">
-        <v>115</v>
+        <v>-24239</v>
       </c>
       <c r="Q44" s="16">
-        <v>0.05</v>
+        <v>-1.17</v>
       </c>
       <c r="R44" s="17" t="inlineStr">
         <is>
-          <t>Commercial Indoor Robotic Vacuums
-Robotic Vacuums</t>
+          <t>Robotic Vacuums</t>
         </is>
       </c>
       <c r="S44" s="18" t="inlineStr">
         <is>
-          <t>5
-16</t>
+          <t>35</t>
         </is>
       </c>
       <c r="T44" s="15">
-        <v>2454</v>
-      </c>
-      <c r="U44" s="16">
-        <v>-0.31</v>
-      </c>
+        <v>207</v>
+      </c>
+      <c r="U44" s="16"/>
       <c r="V44" s="15">
-        <v>73595</v>
-      </c>
-      <c r="W44" s="15" t="inlineStr">
-        <is>
-          <t>2,000</t>
-        </is>
-      </c>
-      <c r="X44" s="15">
-        <v>59980</v>
-      </c>
+        <v>62098</v>
+      </c>
+      <c r="W44" s="15"/>
+      <c r="X44" s="15"/>
       <c r="Y44" s="19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z44" s="20">
-        <v>29.99</v>
+        <v>299.99</v>
       </c>
       <c r="AA44" s="4"/>
       <c r="AB44" s="1"/>
       <c r="AC44" s="2"/>
       <c r="AD44" s="19">
-        <v>1494</v>
+        <v>34</v>
       </c>
       <c r="AE44" s="15">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="AF44" s="21">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="AG44" s="22">
-        <v>0.0073</v>
+        <v>0.019299999999999998</v>
       </c>
       <c r="AH44" s="20">
-        <v>6.31</v>
+        <v>17.21</v>
       </c>
       <c r="AI44" s="16">
-        <v>0.67</v>
+        <v>0.79</v>
       </c>
       <c r="AJ44"/>
       <c r="AK44" s="13" t="inlineStr">
         <is>
-          <t>2023-06-30</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="AL44" s="19">
-        <v>1158</v>
+        <v>15</v>
       </c>
       <c r="AM44" s="13" t="inlineStr">
         <is>
@@ -18163,11 +18065,11 @@
         <v>10</v>
       </c>
       <c r="AR44" s="19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AS44" s="14" t="inlineStr">
         <is>
-          <t>EufyHome</t>
+          <t>Redroad-US</t>
         </is>
       </c>
       <c r="AT44" s="13" t="inlineStr">
@@ -18177,25 +18079,21 @@
       </c>
       <c r="AU44" s="13" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="AV44" s="14" t="inlineStr">
         <is>
-          <t>WA 98004 US</t>
+          <t>福田区福田街道岗厦社区</t>
         </is>
       </c>
       <c r="AW44" s="13" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1U62USFOR8NN3</t>
+          <t>https://www.amazon.com/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1C6K1RF1VZ7JZ</t>
         </is>
       </c>
       <c r="AX44" s="13"/>
-      <c r="AY44" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="AY44" s="13"/>
       <c r="AZ44" s="13"/>
       <c r="BA44" s="13"/>
       <c r="BB44" s="13"/>
@@ -18204,63 +18102,47 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="BD44" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="BD44" s="13"/>
       <c r="BE44" s="13"/>
       <c r="BF44" s="13"/>
       <c r="BG44" s="13"/>
       <c r="BH44" s="14"/>
-      <c r="BI44" s="23" t="inlineStr">
-        <is>
-          <t>Amazon's Choice</t>
-        </is>
-      </c>
+      <c r="BI44" s="23"/>
       <c r="BJ44" s="23" t="inlineStr">
         <is>
-          <t>2.31 pounds</t>
+          <t>1 pounds</t>
         </is>
       </c>
       <c r="BK44" s="23" t="inlineStr">
         <is>
-          <t>1.05 kg</t>
-        </is>
-      </c>
-      <c r="BL44" s="23" t="inlineStr">
-        <is>
-          <t>8.8 x 4.4 x 2 inches</t>
-        </is>
-      </c>
-      <c r="BM44" s="23" t="inlineStr">
-        <is>
-          <t>22.35 x 11.18 x 5.08 cm</t>
-        </is>
-      </c>
+          <t>453.59 g</t>
+        </is>
+      </c>
+      <c r="BL44" s="23"/>
+      <c r="BM44" s="23"/>
       <c r="BN44" s="23" t="inlineStr">
         <is>
-          <t>2.38 pounds</t>
+          <t>15.8 pounds</t>
         </is>
       </c>
       <c r="BO44" s="23" t="inlineStr">
         <is>
-          <t>1.08 kg</t>
+          <t>7.17 kg</t>
         </is>
       </c>
       <c r="BP44" s="23" t="inlineStr">
         <is>
-          <t>8.9 x 4.5 x 4 inches</t>
+          <t>14.9 x 13 x 12.9 inches</t>
         </is>
       </c>
       <c r="BQ44" s="23" t="inlineStr">
         <is>
-          <t>22.61 x 11.43 x 10.16 cm</t>
+          <t>37.85 x 33.02 x 32.77 cm</t>
         </is>
       </c>
       <c r="BR44" s="13" t="inlineStr">
         <is>
-          <t>大号标准尺寸</t>
+          <t>小号大件</t>
         </is>
       </c>
     </row>
@@ -18271,40 +18153,40 @@
       <c r="B45" s="13"/>
       <c r="C45" s="14" t="inlineStr">
         <is>
-          <t>B0GZPM94M2</t>
+          <t>B0HBWDF8XN</t>
         </is>
       </c>
       <c r="D45" s="14"/>
       <c r="E45" s="14"/>
       <c r="F45" s="14" t="inlineStr">
         <is>
-          <t>Redroad</t>
+          <t>UMMUND</t>
         </is>
       </c>
       <c r="G45" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Redroad</t>
+          <t>https://www.amazon.com/stores/UMMUNDRobotVaccuumandMop/page/E436C8FC-A6A3-4981-93C0-1497D6853AF8?lp_asin=B0HBWDF8XN&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
         </is>
       </c>
       <c r="H45" s="14" t="inlineStr">
         <is>
-          <t>Redroad Robot Vacuum 20,000Pa Robot Vacuum Mop,120Day Self Emptying Vacuum Robot,Lidar Navigation,2.4G 5G WiFi APP Aspirateur</t>
+          <t>UMMUND Robot Vacuum and Mop Combo, 8000Pa Strong Suction 2 in 1 Vacuum Robot with Mopping, with Schedule, Wi-Fi/App/Remote, S</t>
         </is>
       </c>
       <c r="I45" s="14"/>
       <c r="J45" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/dp/B0GZPM94M2?psc=1</t>
+          <t>https://www.amazon.com/dp/B0HBWDF8XN?psc=1</t>
         </is>
       </c>
       <c r="K45" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/71GaguO8jGL._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/811PjBfyLYL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L45" s="14" t="inlineStr">
         <is>
-          <t>B0GZPM94M2</t>
+          <t>B0HBWDF8XN</t>
         </is>
       </c>
       <c r="M45" s="14" t="inlineStr">
@@ -18318,13 +18200,13 @@
         </is>
       </c>
       <c r="O45" s="15">
-        <v>31155</v>
+        <v>53428</v>
       </c>
       <c r="P45" s="15">
-        <v>-24239</v>
+        <v>-39905</v>
       </c>
       <c r="Q45" s="16">
-        <v>-1.17</v>
+        <v>-2.95</v>
       </c>
       <c r="R45" s="17" t="inlineStr">
         <is>
@@ -18333,15 +18215,15 @@
       </c>
       <c r="S45" s="18" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>49</t>
         </is>
       </c>
       <c r="T45" s="15">
-        <v>207</v>
+        <v>296</v>
       </c>
       <c r="U45" s="16"/>
       <c r="V45" s="15">
-        <v>62098</v>
+        <v>37293</v>
       </c>
       <c r="W45" s="15"/>
       <c r="X45" s="15"/>
@@ -18349,37 +18231,37 @@
         <v>1</v>
       </c>
       <c r="Z45" s="20">
-        <v>299.99</v>
+        <v>125.99</v>
       </c>
       <c r="AA45" s="4"/>
       <c r="AB45" s="1"/>
       <c r="AC45" s="2"/>
       <c r="AD45" s="19">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="AE45" s="15">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AF45" s="21">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="AG45" s="22">
-        <v>0.019299999999999998</v>
+        <v>0.0068000000000000005</v>
       </c>
       <c r="AH45" s="20">
-        <v>17.21</v>
+        <v>9.08</v>
       </c>
       <c r="AI45" s="16">
-        <v>0.79</v>
+        <v>0.78</v>
       </c>
       <c r="AJ45"/>
       <c r="AK45" s="13" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="AL45" s="19">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AM45" s="13" t="inlineStr">
         <is>
@@ -18397,7 +18279,7 @@
       </c>
       <c r="AS45" s="14" t="inlineStr">
         <is>
-          <t>Redroad-US</t>
+          <t>Zhuina11</t>
         </is>
       </c>
       <c r="AT45" s="13" t="inlineStr">
@@ -18407,30 +18289,38 @@
       </c>
       <c r="AU45" s="13" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>CN(HK)</t>
         </is>
       </c>
       <c r="AV45" s="14" t="inlineStr">
         <is>
-          <t>福田区福田街道岗厦社区</t>
+          <t>KOWLOON HONG KONG 999077 HK</t>
         </is>
       </c>
       <c r="AW45" s="13" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1C6K1RF1VZ7JZ</t>
+          <t>https://www.amazon.com/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3TSG3NHMTCHQR</t>
         </is>
       </c>
       <c r="AX45" s="13"/>
       <c r="AY45" s="13"/>
       <c r="AZ45" s="13"/>
       <c r="BA45" s="13"/>
-      <c r="BB45" s="13"/>
+      <c r="BB45" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="BC45" s="13" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="BD45" s="13"/>
+      <c r="BD45" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="BE45" s="13"/>
       <c r="BF45" s="13"/>
       <c r="BG45" s="13"/>
@@ -18438,39 +18328,47 @@
       <c r="BI45" s="23"/>
       <c r="BJ45" s="23" t="inlineStr">
         <is>
-          <t>1 pounds</t>
+          <t>7.28 pounds</t>
         </is>
       </c>
       <c r="BK45" s="23" t="inlineStr">
         <is>
-          <t>453.59 g</t>
-        </is>
-      </c>
-      <c r="BL45" s="23"/>
-      <c r="BM45" s="23"/>
+          <t>3.30 kg</t>
+        </is>
+      </c>
+      <c r="BL45" s="23" t="inlineStr">
+        <is>
+          <t>12.1 x 12.1 x 3.2 inches</t>
+        </is>
+      </c>
+      <c r="BM45" s="23" t="inlineStr">
+        <is>
+          <t>30.73 x 30.73 x 8.13 cm</t>
+        </is>
+      </c>
       <c r="BN45" s="23" t="inlineStr">
         <is>
-          <t>15.8 pounds</t>
+          <t>7.32 pounds</t>
         </is>
       </c>
       <c r="BO45" s="23" t="inlineStr">
         <is>
-          <t>7.17 kg</t>
+          <t>3.32 kg</t>
         </is>
       </c>
       <c r="BP45" s="23" t="inlineStr">
         <is>
-          <t>14.9 x 13 x 12.9 inches</t>
+          <t>15.8 x 13.6 x 4.3 inches</t>
         </is>
       </c>
       <c r="BQ45" s="23" t="inlineStr">
         <is>
-          <t>37.85 x 33.02 x 32.77 cm</t>
+          <t>40.13 x 34.54 x 10.92 cm</t>
         </is>
       </c>
       <c r="BR45" s="13" t="inlineStr">
         <is>
-          <t>小号大件</t>
+          <t>大号标准尺寸</t>
         </is>
       </c>
     </row>
@@ -18481,131 +18379,119 @@
       <c r="B46" s="13"/>
       <c r="C46" s="14" t="inlineStr">
         <is>
-          <t>B0BCF8N3B4</t>
+          <t>B0GWH7M8L9</t>
         </is>
       </c>
       <c r="D46" s="14"/>
       <c r="E46" s="14"/>
       <c r="F46" s="14" t="inlineStr">
         <is>
-          <t>ECOVACS</t>
+          <t>BOTLUXE</t>
         </is>
       </c>
       <c r="G46" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/stores/ECOVACS/page/E74F14EC-79FC-433B-8BB9-DA6190E35D28?lp_asin=B0BCF8N3B4&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.com/stores/BOTLUXE/page/5E044AA6-CC48-4FCC-B008-B011598BBA8B?lp_asin=B0GWH7M8L9&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
         </is>
       </c>
       <c r="H46" s="14" t="inlineStr">
         <is>
-          <t>ECOVACS Multi-Surface Floor Cleaning Solution, Compatible with DEEBOT X11 OMNI Cyclone / X9 PRO OMNI / T80 OMNI / T50 PRO OMN</t>
+          <t>BOTLUXE Robot Vacuum and Mop Self-Emptying with 8,000Pa Suction, LiDAR Navigation, Home Mapping, 75-Day Capacity, No-Go Zones</t>
         </is>
       </c>
       <c r="I46" s="14"/>
       <c r="J46" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/dp/B0BCF8N3B4?psc=1</t>
+          <t>https://www.amazon.com/dp/B0GWH7M8L9?psc=1</t>
         </is>
       </c>
       <c r="K46" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/51OKmAG4ODL._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/71mRKmu7xhL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L46" s="14" t="inlineStr">
         <is>
-          <t>B0BCF8N3B4</t>
+          <t>B0GWH7M8L9</t>
         </is>
       </c>
       <c r="M46" s="14" t="inlineStr">
         <is>
-          <t>Industrial &amp; Scientific:Janitorial &amp; Sanitation Supplies:Vacuums &amp; Floor Cleaning Machines:Vacuums:Robotic Vacuums</t>
+          <t>Home &amp; Kitchen:Vacuums &amp; Floor Care:Vacuums:Robotic Vacuums</t>
         </is>
       </c>
       <c r="N46" s="14" t="inlineStr">
         <is>
-          <t>Industrial &amp; Scientific</t>
+          <t>Home &amp; Kitchen</t>
         </is>
       </c>
       <c r="O46" s="15">
-        <v>2639</v>
+        <v>36746</v>
       </c>
       <c r="P46" s="15">
-        <v>-40</v>
+        <v>2278737</v>
       </c>
       <c r="Q46" s="16">
-        <v>-0.02</v>
+        <v>0.98</v>
       </c>
       <c r="R46" s="17" t="inlineStr">
         <is>
-          <t>Commercial Indoor Robotic Vacuums
-Robotic Vacuums</t>
+          <t>Robotic Vacuums</t>
         </is>
       </c>
       <c r="S46" s="18" t="inlineStr">
         <is>
-          <t>6
-18</t>
+          <t>36</t>
         </is>
       </c>
       <c r="T46" s="15">
-        <v>2067</v>
-      </c>
-      <c r="U46" s="16">
-        <v>0.17</v>
-      </c>
+        <v>90</v>
+      </c>
+      <c r="U46" s="16"/>
       <c r="V46" s="15">
-        <v>51654</v>
-      </c>
-      <c r="W46" s="15" t="inlineStr">
-        <is>
-          <t>2,000</t>
-        </is>
-      </c>
-      <c r="X46" s="15">
-        <v>49440</v>
-      </c>
+        <v>33299</v>
+      </c>
+      <c r="W46" s="15"/>
+      <c r="X46" s="15"/>
       <c r="Y46" s="19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z46" s="20">
-        <v>24.99</v>
+        <v>369.99</v>
       </c>
       <c r="AA46" s="4"/>
       <c r="AB46" s="1"/>
-      <c r="AC46" s="2">
-        <v>3</v>
-      </c>
+      <c r="AC46" s="2"/>
       <c r="AD46" s="19">
-        <v>1193</v>
+        <v>20</v>
       </c>
       <c r="AE46" s="15">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="AF46" s="21">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="AG46" s="22">
-        <v>0.0077</v>
+        <v>0.11109999999999999</v>
       </c>
       <c r="AH46" s="20">
-        <v>6.48</v>
+        <v>20.28</v>
       </c>
       <c r="AI46" s="16">
-        <v>0.62</v>
+        <v>0.8</v>
       </c>
       <c r="AJ46"/>
       <c r="AK46" s="13" t="inlineStr">
         <is>
-          <t>2023-02-17</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="AL46" s="19">
-        <v>1290</v>
+        <v>16</v>
       </c>
       <c r="AM46" s="13" t="inlineStr">
         <is>
-          <t>AMZ</t>
+          <t>FBA</t>
         </is>
       </c>
       <c r="AN46" s="13"/>
@@ -18619,23 +18505,31 @@
       </c>
       <c r="AS46" s="14" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>Yy offical store</t>
         </is>
       </c>
       <c r="AT46" s="13" t="inlineStr">
         <is>
-          <t>AMZ</t>
-        </is>
-      </c>
-      <c r="AU46" s="13"/>
-      <c r="AV46" s="14"/>
-      <c r="AW46" s="13"/>
+          <t>FBA</t>
+        </is>
+      </c>
+      <c r="AU46" s="13" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="AV46" s="14" t="inlineStr">
+        <is>
+          <t>福田区福田街道岗厦社区彩田路3069号</t>
+        </is>
+      </c>
+      <c r="AW46" s="13" t="inlineStr">
+        <is>
+          <t>https://www.amazon.com/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2KXKLM92VNJJ5</t>
+        </is>
+      </c>
       <c r="AX46" s="13"/>
-      <c r="AY46" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="AY46" s="13"/>
       <c r="AZ46" s="13"/>
       <c r="BA46" s="13"/>
       <c r="BB46" s="13"/>
@@ -18644,59 +18538,59 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="BD46" s="13"/>
+      <c r="BD46" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="BE46" s="13"/>
       <c r="BF46" s="13"/>
       <c r="BG46" s="13"/>
       <c r="BH46" s="14"/>
-      <c r="BI46" s="23" t="inlineStr">
-        <is>
-          <t>Amazon's Choice</t>
-        </is>
-      </c>
+      <c r="BI46" s="23"/>
       <c r="BJ46" s="23" t="inlineStr">
         <is>
-          <t>2.69 pounds</t>
+          <t>14.57 pounds</t>
         </is>
       </c>
       <c r="BK46" s="23" t="inlineStr">
         <is>
-          <t>1.22 kg</t>
+          <t>6.61 kg</t>
         </is>
       </c>
       <c r="BL46" s="23" t="inlineStr">
         <is>
-          <t>3.5 x 3.5 x 9.7 inches</t>
+          <t>14 x 6 x 10 inches</t>
         </is>
       </c>
       <c r="BM46" s="23" t="inlineStr">
         <is>
-          <t>8.89 x 8.89 x 24.64 cm</t>
+          <t>35.56 x 15.24 x 25.40 cm</t>
         </is>
       </c>
       <c r="BN46" s="23" t="inlineStr">
         <is>
-          <t>2.62 pounds</t>
+          <t>14.6 pounds</t>
         </is>
       </c>
       <c r="BO46" s="23" t="inlineStr">
         <is>
-          <t>1.19 kg</t>
+          <t>6.62 kg</t>
         </is>
       </c>
       <c r="BP46" s="23" t="inlineStr">
         <is>
-          <t>9.7 x 3.5 x 3.5 inches</t>
+          <t>16 x 15 x 14 inches</t>
         </is>
       </c>
       <c r="BQ46" s="23" t="inlineStr">
         <is>
-          <t>24.64 x 8.89 x 8.89 cm</t>
+          <t>40.64 x 38.10 x 35.56 cm</t>
         </is>
       </c>
       <c r="BR46" s="13" t="inlineStr">
         <is>
-          <t>大号标准尺寸</t>
+          <t>小号大件</t>
         </is>
       </c>
     </row>
@@ -18707,40 +18601,40 @@
       <c r="B47" s="13"/>
       <c r="C47" s="14" t="inlineStr">
         <is>
-          <t>B0HBWDF8XN</t>
+          <t>B0BVQC5P6W</t>
         </is>
       </c>
       <c r="D47" s="14"/>
       <c r="E47" s="14"/>
       <c r="F47" s="14" t="inlineStr">
         <is>
-          <t>UMMUND</t>
+          <t>roborock</t>
         </is>
       </c>
       <c r="G47" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/stores/UMMUNDRobotVaccuumandMop/page/E436C8FC-A6A3-4981-93C0-1497D6853AF8?lp_asin=B0HBWDF8XN&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.com/stores/Roborock/page/69ADA24D-41D1-454D-9AAC-68D2B6252352?lp_asin=B0BVQC5P6W&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
         </is>
       </c>
       <c r="H47" s="14" t="inlineStr">
         <is>
-          <t>UMMUND Robot Vacuum and Mop Combo, 8000Pa Strong Suction 2 in 1 Vacuum Robot with Mopping, with Schedule, Wi-Fi/App/Remote, S</t>
+          <t>roborock Side Brushes Replacement (2 Pieces) for S8 Pro Ultra, S7 Max Ultra, Qrevo, Roborock Qrevo Slim, Series of S7 MaxV/S7</t>
         </is>
       </c>
       <c r="I47" s="14"/>
       <c r="J47" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/dp/B0HBWDF8XN?psc=1</t>
+          <t>https://www.amazon.com/dp/B0BVQC5P6W?psc=1</t>
         </is>
       </c>
       <c r="K47" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/811PjBfyLYL._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/41954aVFRAL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L47" s="14" t="inlineStr">
         <is>
-          <t>B0HBWDF8XN</t>
+          <t>B0BVQC5P6W</t>
         </is>
       </c>
       <c r="M47" s="14" t="inlineStr">
@@ -18754,13 +18648,13 @@
         </is>
       </c>
       <c r="O47" s="15">
-        <v>53428</v>
+        <v>32313</v>
       </c>
       <c r="P47" s="15">
-        <v>-39905</v>
+        <v>12987</v>
       </c>
       <c r="Q47" s="16">
-        <v>-2.95</v>
+        <v>0.29</v>
       </c>
       <c r="R47" s="17" t="inlineStr">
         <is>
@@ -18769,53 +18663,63 @@
       </c>
       <c r="S47" s="18" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>36</t>
         </is>
       </c>
       <c r="T47" s="15">
-        <v>296</v>
-      </c>
-      <c r="U47" s="16"/>
+        <v>1040</v>
+      </c>
+      <c r="U47" s="16">
+        <v>-0.22</v>
+      </c>
       <c r="V47" s="15">
-        <v>37293</v>
-      </c>
-      <c r="W47" s="15"/>
-      <c r="X47" s="15"/>
+        <v>16630</v>
+      </c>
+      <c r="W47" s="15" t="inlineStr">
+        <is>
+          <t>800</t>
+        </is>
+      </c>
+      <c r="X47" s="15">
+        <v>12792</v>
+      </c>
       <c r="Y47" s="19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z47" s="20">
-        <v>125.99</v>
+        <v>15.99</v>
       </c>
       <c r="AA47" s="4"/>
       <c r="AB47" s="1"/>
-      <c r="AC47" s="2"/>
+      <c r="AC47" s="2">
+        <v>23</v>
+      </c>
       <c r="AD47" s="19">
-        <v>33</v>
+        <v>857</v>
       </c>
       <c r="AE47" s="15">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="AF47" s="21">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="AG47" s="22">
-        <v>0.0068000000000000005</v>
+        <v>0.0106</v>
       </c>
       <c r="AH47" s="20">
-        <v>9.08</v>
+        <v>4.09</v>
       </c>
       <c r="AI47" s="16">
-        <v>0.78</v>
+        <v>0.59</v>
       </c>
       <c r="AJ47"/>
       <c r="AK47" s="13" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2023-04-04</t>
         </is>
       </c>
       <c r="AL47" s="19">
-        <v>17</v>
+        <v>1244</v>
       </c>
       <c r="AM47" s="13" t="inlineStr">
         <is>
@@ -18833,7 +18737,7 @@
       </c>
       <c r="AS47" s="14" t="inlineStr">
         <is>
-          <t>Zhuina11</t>
+          <t>Roborock Technology Co. Ltd</t>
         </is>
       </c>
       <c r="AT47" s="13" t="inlineStr">
@@ -18848,76 +18752,80 @@
       </c>
       <c r="AV47" s="14" t="inlineStr">
         <is>
-          <t>KOWLOON HONG KONG 999077 HK</t>
+          <t>SHEUNG WAN HK 999077 HK</t>
         </is>
       </c>
       <c r="AW47" s="13" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3TSG3NHMTCHQR</t>
-        </is>
-      </c>
-      <c r="AX47" s="13"/>
-      <c r="AY47" s="13"/>
+          <t>https://www.amazon.com/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2NZXCP1D8DIIH</t>
+        </is>
+      </c>
+      <c r="AX47" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="AY47" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="AZ47" s="13"/>
       <c r="BA47" s="13"/>
-      <c r="BB47" s="13" t="inlineStr">
+      <c r="BB47" s="13"/>
+      <c r="BC47" s="13" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="BC47" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="BD47" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="BD47" s="13"/>
       <c r="BE47" s="13"/>
       <c r="BF47" s="13"/>
       <c r="BG47" s="13"/>
       <c r="BH47" s="14"/>
-      <c r="BI47" s="23"/>
+      <c r="BI47" s="23" t="inlineStr">
+        <is>
+          <t>Amazon's Choice</t>
+        </is>
+      </c>
       <c r="BJ47" s="23" t="inlineStr">
         <is>
-          <t>7.28 pounds</t>
+          <t>1.76 ounces</t>
         </is>
       </c>
       <c r="BK47" s="23" t="inlineStr">
         <is>
-          <t>3.30 kg</t>
+          <t>49.90 g</t>
         </is>
       </c>
       <c r="BL47" s="23" t="inlineStr">
         <is>
-          <t>12.1 x 12.1 x 3.2 inches</t>
+          <t>2.4 x 2.4 x 0.4 inches</t>
         </is>
       </c>
       <c r="BM47" s="23" t="inlineStr">
         <is>
-          <t>30.73 x 30.73 x 8.13 cm</t>
+          <t>6.10 x 6.10 x 1.02 cm</t>
         </is>
       </c>
       <c r="BN47" s="23" t="inlineStr">
         <is>
-          <t>7.32 pounds</t>
+          <t>0.11 pounds</t>
         </is>
       </c>
       <c r="BO47" s="23" t="inlineStr">
         <is>
-          <t>3.32 kg</t>
+          <t>49.90 g</t>
         </is>
       </c>
       <c r="BP47" s="23" t="inlineStr">
         <is>
-          <t>15.8 x 13.6 x 4.3 inches</t>
+          <t>4.6 x 4.6 x 2 inches</t>
         </is>
       </c>
       <c r="BQ47" s="23" t="inlineStr">
         <is>
-          <t>40.13 x 34.54 x 10.92 cm</t>
+          <t>11.68 x 11.68 x 5.08 cm</t>
         </is>
       </c>
       <c r="BR47" s="13" t="inlineStr">
@@ -18933,40 +18841,40 @@
       <c r="B48" s="13"/>
       <c r="C48" s="14" t="inlineStr">
         <is>
-          <t>B0GWH7M8L9</t>
+          <t>B0HFCGGZSH</t>
         </is>
       </c>
       <c r="D48" s="14"/>
       <c r="E48" s="14"/>
       <c r="F48" s="14" t="inlineStr">
         <is>
-          <t>BOTLUXE</t>
+          <t>ZC WAS</t>
         </is>
       </c>
       <c r="G48" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/stores/BOTLUXE/page/5E044AA6-CC48-4FCC-B008-B011598BBA8B?lp_asin=B0GWH7M8L9&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.com/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=ZC+WAS</t>
         </is>
       </c>
       <c r="H48" s="14" t="inlineStr">
         <is>
-          <t>BOTLUXE Robot Vacuum and Mop Self-Emptying with 8,000Pa Suction, LiDAR Navigation, Home Mapping, 75-Day Capacity, No-Go Zones</t>
+          <t>ZC WAS Robot Vacuum and Mop for Pet Hair, 2-in-1 Robot Vacuum Cleaner for Hard Floors&amp;Carpets with 2.87'' Slim Design, Wi-Fi/</t>
         </is>
       </c>
       <c r="I48" s="14"/>
       <c r="J48" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/dp/B0GWH7M8L9?psc=1</t>
+          <t>https://www.amazon.com/dp/B0HFCGGZSH?psc=1</t>
         </is>
       </c>
       <c r="K48" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/71mRKmu7xhL._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/81uJWk6uyXL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L48" s="14" t="inlineStr">
         <is>
-          <t>B0GWH7M8L9</t>
+          <t>B0HFCGGZSH</t>
         </is>
       </c>
       <c r="M48" s="14" t="inlineStr">
@@ -18980,13 +18888,11 @@
         </is>
       </c>
       <c r="O48" s="15">
-        <v>36746</v>
-      </c>
-      <c r="P48" s="15">
-        <v>2278737</v>
-      </c>
+        <v>69037</v>
+      </c>
+      <c r="P48" s="15"/>
       <c r="Q48" s="16">
-        <v>0.98</v>
+        <v>0</v>
       </c>
       <c r="R48" s="17" t="inlineStr">
         <is>
@@ -18995,15 +18901,15 @@
       </c>
       <c r="S48" s="18" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>56</t>
         </is>
       </c>
       <c r="T48" s="15">
-        <v>90</v>
+        <v>52</v>
       </c>
       <c r="U48" s="16"/>
       <c r="V48" s="15">
-        <v>33299</v>
+        <v>5719</v>
       </c>
       <c r="W48" s="15"/>
       <c r="X48" s="15"/>
@@ -19011,37 +18917,37 @@
         <v>1</v>
       </c>
       <c r="Z48" s="20">
-        <v>369.99</v>
+        <v>109.99</v>
       </c>
       <c r="AA48" s="4"/>
       <c r="AB48" s="1"/>
       <c r="AC48" s="2"/>
       <c r="AD48" s="19">
-        <v>20</v>
+        <v>157</v>
       </c>
       <c r="AE48" s="15">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AF48" s="21">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="AG48" s="22">
-        <v>0.11109999999999999</v>
+        <v>0</v>
       </c>
       <c r="AH48" s="20">
-        <v>20.28</v>
+        <v>9.5</v>
       </c>
       <c r="AI48" s="16">
-        <v>0.8</v>
+        <v>0.76</v>
       </c>
       <c r="AJ48"/>
       <c r="AK48" s="13" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="AL48" s="19">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AM48" s="13" t="inlineStr">
         <is>
@@ -19059,7 +18965,7 @@
       </c>
       <c r="AS48" s="14" t="inlineStr">
         <is>
-          <t>Yy offical store</t>
+          <t>biao ge</t>
         </is>
       </c>
       <c r="AT48" s="13" t="inlineStr">
@@ -19074,12 +18980,12 @@
       </c>
       <c r="AV48" s="14" t="inlineStr">
         <is>
-          <t>福田区福田街道岗厦社区彩田路3069号</t>
+          <t>广东省东莞市黄江镇</t>
         </is>
       </c>
       <c r="AW48" s="13" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2KXKLM92VNJJ5</t>
+          <t>https://www.amazon.com/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2UKVTD4STWRQG</t>
         </is>
       </c>
       <c r="AX48" s="13"/>
@@ -19104,47 +19010,47 @@
       <c r="BI48" s="23"/>
       <c r="BJ48" s="23" t="inlineStr">
         <is>
-          <t>14.57 pounds</t>
+          <t>7.7 pounds</t>
         </is>
       </c>
       <c r="BK48" s="23" t="inlineStr">
         <is>
-          <t>6.61 kg</t>
+          <t>3.49 kg</t>
         </is>
       </c>
       <c r="BL48" s="23" t="inlineStr">
         <is>
-          <t>14 x 6 x 10 inches</t>
+          <t>11.8 x 2.9 x 11.8 inches</t>
         </is>
       </c>
       <c r="BM48" s="23" t="inlineStr">
         <is>
-          <t>35.56 x 15.24 x 25.40 cm</t>
+          <t>29.97 x 7.37 x 29.97 cm</t>
         </is>
       </c>
       <c r="BN48" s="23" t="inlineStr">
         <is>
-          <t>14.6 pounds</t>
+          <t>7.72 pounds</t>
         </is>
       </c>
       <c r="BO48" s="23" t="inlineStr">
         <is>
-          <t>6.62 kg</t>
+          <t>3.50 kg</t>
         </is>
       </c>
       <c r="BP48" s="23" t="inlineStr">
         <is>
-          <t>16 x 15 x 14 inches</t>
+          <t>16.9 x 13.7 x 5.3 inches</t>
         </is>
       </c>
       <c r="BQ48" s="23" t="inlineStr">
         <is>
-          <t>40.64 x 38.10 x 35.56 cm</t>
+          <t>42.93 x 34.80 x 13.46 cm</t>
         </is>
       </c>
       <c r="BR48" s="13" t="inlineStr">
         <is>
-          <t>小号大件</t>
+          <t>大号标准尺寸</t>
         </is>
       </c>
     </row>
@@ -19155,40 +19061,40 @@
       <c r="B49" s="13"/>
       <c r="C49" s="14" t="inlineStr">
         <is>
-          <t>B0BVQC5P6W</t>
+          <t>B07RG7X3Q9</t>
         </is>
       </c>
       <c r="D49" s="14"/>
       <c r="E49" s="14"/>
       <c r="F49" s="14" t="inlineStr">
         <is>
-          <t>roborock</t>
+          <t>iRobot</t>
         </is>
       </c>
       <c r="G49" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/stores/Roborock/page/69ADA24D-41D1-454D-9AAC-68D2B6252352?lp_asin=B0BVQC5P6W&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.com/stores/iRobot%C2%AE/page/A144A34F-3D29-45A4-9DF7-8E77C31F8C7F?lp_asin=B07RG7X3Q9&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
         </is>
       </c>
       <c r="H49" s="14" t="inlineStr">
         <is>
-          <t>roborock Side Brushes Replacement (2 Pieces) for S8 Pro Ultra, S7 Max Ultra, Qrevo, Roborock Qrevo Slim, Series of S7 MaxV/S7</t>
+          <t>iRobot® Authentic Replacement Parts- Braava Jet® m Series Dry Sweeping Pads, (7-Pack)</t>
         </is>
       </c>
       <c r="I49" s="14"/>
       <c r="J49" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/dp/B0BVQC5P6W?psc=1</t>
+          <t>https://www.amazon.com/dp/B07RG7X3Q9?psc=1</t>
         </is>
       </c>
       <c r="K49" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/41954aVFRAL._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/717-XciGC4L._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L49" s="14" t="inlineStr">
         <is>
-          <t>B0BVQC5P6W</t>
+          <t>B07RG7X3Q9</t>
         </is>
       </c>
       <c r="M49" s="14" t="inlineStr">
@@ -19202,82 +19108,84 @@
         </is>
       </c>
       <c r="O49" s="15">
-        <v>32313</v>
+        <v>51739</v>
       </c>
       <c r="P49" s="15">
-        <v>12987</v>
+        <v>23857</v>
       </c>
       <c r="Q49" s="16">
-        <v>0.29</v>
+        <v>0.32</v>
       </c>
       <c r="R49" s="17" t="inlineStr">
         <is>
-          <t>Robotic Vacuums</t>
+          <t>Sweepers &amp; Accessories
+Robotic Vacuums</t>
         </is>
       </c>
       <c r="S49" s="18" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>19
+49</t>
         </is>
       </c>
       <c r="T49" s="15">
-        <v>1040</v>
+        <v>467</v>
       </c>
       <c r="U49" s="16">
-        <v>-0.22</v>
+        <v>2.53</v>
       </c>
       <c r="V49" s="15">
-        <v>16630</v>
+        <v>3358</v>
       </c>
       <c r="W49" s="15" t="inlineStr">
         <is>
-          <t>800</t>
+          <t>400</t>
         </is>
       </c>
       <c r="X49" s="15">
-        <v>12792</v>
+        <v>3196</v>
       </c>
       <c r="Y49" s="19">
         <v>2</v>
       </c>
       <c r="Z49" s="20">
-        <v>15.99</v>
+        <v>7.99</v>
       </c>
       <c r="AA49" s="4"/>
       <c r="AB49" s="1"/>
       <c r="AC49" s="2">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="AD49" s="19">
-        <v>857</v>
+        <v>1805</v>
       </c>
       <c r="AE49" s="15">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="AF49" s="21">
         <v>4.7</v>
       </c>
       <c r="AG49" s="22">
-        <v>0.0106</v>
+        <v>0.015</v>
       </c>
       <c r="AH49" s="20">
-        <v>4.09</v>
+        <v>3.91</v>
       </c>
       <c r="AI49" s="16">
-        <v>0.59</v>
+        <v>0.31</v>
       </c>
       <c r="AJ49"/>
       <c r="AK49" s="13" t="inlineStr">
         <is>
-          <t>2023-04-04</t>
+          <t>2019-06-10</t>
         </is>
       </c>
       <c r="AL49" s="19">
-        <v>1244</v>
+        <v>2638</v>
       </c>
       <c r="AM49" s="13" t="inlineStr">
         <is>
-          <t>FBA</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="AN49" s="13"/>
@@ -19291,39 +19199,19 @@
       </c>
       <c r="AS49" s="14" t="inlineStr">
         <is>
-          <t>Roborock Technology Co. Ltd</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="AT49" s="13" t="inlineStr">
         <is>
-          <t>FBA</t>
-        </is>
-      </c>
-      <c r="AU49" s="13" t="inlineStr">
-        <is>
-          <t>CN(HK)</t>
-        </is>
-      </c>
-      <c r="AV49" s="14" t="inlineStr">
-        <is>
-          <t>SHEUNG WAN HK 999077 HK</t>
-        </is>
-      </c>
-      <c r="AW49" s="13" t="inlineStr">
-        <is>
-          <t>https://www.amazon.com/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2NZXCP1D8DIIH</t>
-        </is>
-      </c>
-      <c r="AX49" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="AY49" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AU49" s="13"/>
+      <c r="AV49" s="14"/>
+      <c r="AW49" s="13"/>
+      <c r="AX49" s="13"/>
+      <c r="AY49" s="13"/>
       <c r="AZ49" s="13"/>
       <c r="BA49" s="13"/>
       <c r="BB49" s="13"/>
@@ -19332,499 +19220,57 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="BD49" s="13"/>
+      <c r="BD49" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="BE49" s="13"/>
       <c r="BF49" s="13"/>
       <c r="BG49" s="13"/>
       <c r="BH49" s="14"/>
-      <c r="BI49" s="23" t="inlineStr">
-        <is>
-          <t>Amazon's Choice</t>
-        </is>
-      </c>
+      <c r="BI49" s="23"/>
       <c r="BJ49" s="23" t="inlineStr">
         <is>
-          <t>1.76 ounces</t>
+          <t>0.05 pounds</t>
         </is>
       </c>
       <c r="BK49" s="23" t="inlineStr">
         <is>
-          <t>49.90 g</t>
+          <t>22.68 g</t>
         </is>
       </c>
       <c r="BL49" s="23" t="inlineStr">
         <is>
-          <t>2.4 x 2.4 x 0.4 inches</t>
+          <t>4.2 x 10.6 x 0.3 inches</t>
         </is>
       </c>
       <c r="BM49" s="23" t="inlineStr">
         <is>
-          <t>6.10 x 6.10 x 1.02 cm</t>
+          <t>10.67 x 26.92 x 0.76 cm</t>
         </is>
       </c>
       <c r="BN49" s="23" t="inlineStr">
         <is>
-          <t>0.11 pounds</t>
+          <t>0.44 pounds</t>
         </is>
       </c>
       <c r="BO49" s="23" t="inlineStr">
         <is>
-          <t>49.90 g</t>
+          <t>199.58 g</t>
         </is>
       </c>
       <c r="BP49" s="23" t="inlineStr">
         <is>
-          <t>4.6 x 4.6 x 2 inches</t>
+          <t>11.1 x 4.7 x 2.5 inches</t>
         </is>
       </c>
       <c r="BQ49" s="23" t="inlineStr">
         <is>
-          <t>11.68 x 11.68 x 5.08 cm</t>
+          <t>28.19 x 11.94 x 6.35 cm</t>
         </is>
       </c>
       <c r="BR49" s="13" t="inlineStr">
-        <is>
-          <t>大号标准尺寸</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="13">
-        <v>49</v>
-      </c>
-      <c r="B50" s="13"/>
-      <c r="C50" s="14" t="inlineStr">
-        <is>
-          <t>B0HFCGGZSH</t>
-        </is>
-      </c>
-      <c r="D50" s="14"/>
-      <c r="E50" s="14"/>
-      <c r="F50" s="14" t="inlineStr">
-        <is>
-          <t>ZC WAS</t>
-        </is>
-      </c>
-      <c r="G50" s="14" t="inlineStr">
-        <is>
-          <t>https://www.amazon.com/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=ZC+WAS</t>
-        </is>
-      </c>
-      <c r="H50" s="14" t="inlineStr">
-        <is>
-          <t>ZC WAS Robot Vacuum and Mop for Pet Hair, 2-in-1 Robot Vacuum Cleaner for Hard Floors&amp;Carpets with 2.87'' Slim Design, Wi-Fi/</t>
-        </is>
-      </c>
-      <c r="I50" s="14"/>
-      <c r="J50" s="14" t="inlineStr">
-        <is>
-          <t>https://www.amazon.com/dp/B0HFCGGZSH?psc=1</t>
-        </is>
-      </c>
-      <c r="K50" s="14" t="inlineStr">
-        <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/81uJWk6uyXL._AC_US600_.jpg</t>
-        </is>
-      </c>
-      <c r="L50" s="14" t="inlineStr">
-        <is>
-          <t>B0HFCGGZSH</t>
-        </is>
-      </c>
-      <c r="M50" s="14" t="inlineStr">
-        <is>
-          <t>Home &amp; Kitchen:Vacuums &amp; Floor Care:Vacuums:Robotic Vacuums</t>
-        </is>
-      </c>
-      <c r="N50" s="14" t="inlineStr">
-        <is>
-          <t>Home &amp; Kitchen</t>
-        </is>
-      </c>
-      <c r="O50" s="15">
-        <v>69037</v>
-      </c>
-      <c r="P50" s="15"/>
-      <c r="Q50" s="16">
-        <v>0</v>
-      </c>
-      <c r="R50" s="17" t="inlineStr">
-        <is>
-          <t>Robotic Vacuums</t>
-        </is>
-      </c>
-      <c r="S50" s="18" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="T50" s="15">
-        <v>52</v>
-      </c>
-      <c r="U50" s="16"/>
-      <c r="V50" s="15">
-        <v>5719</v>
-      </c>
-      <c r="W50" s="15"/>
-      <c r="X50" s="15"/>
-      <c r="Y50" s="19">
-        <v>1</v>
-      </c>
-      <c r="Z50" s="20">
-        <v>109.99</v>
-      </c>
-      <c r="AA50" s="4"/>
-      <c r="AB50" s="1"/>
-      <c r="AC50" s="2"/>
-      <c r="AD50" s="19">
-        <v>157</v>
-      </c>
-      <c r="AE50" s="15">
-        <v>0</v>
-      </c>
-      <c r="AF50" s="21">
-        <v>4.9</v>
-      </c>
-      <c r="AG50" s="22">
-        <v>0</v>
-      </c>
-      <c r="AH50" s="20">
-        <v>9.5</v>
-      </c>
-      <c r="AI50" s="16">
-        <v>0.76</v>
-      </c>
-      <c r="AJ50"/>
-      <c r="AK50" s="13" t="inlineStr">
-        <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="AL50" s="19">
-        <v>13</v>
-      </c>
-      <c r="AM50" s="13" t="inlineStr">
-        <is>
-          <t>FBA</t>
-        </is>
-      </c>
-      <c r="AN50" s="13"/>
-      <c r="AO50" s="13"/>
-      <c r="AP50" s="4"/>
-      <c r="AQ50" s="19">
-        <v>10</v>
-      </c>
-      <c r="AR50" s="19">
-        <v>1</v>
-      </c>
-      <c r="AS50" s="14" t="inlineStr">
-        <is>
-          <t>biao ge</t>
-        </is>
-      </c>
-      <c r="AT50" s="13" t="inlineStr">
-        <is>
-          <t>FBA</t>
-        </is>
-      </c>
-      <c r="AU50" s="13" t="inlineStr">
-        <is>
-          <t>CN</t>
-        </is>
-      </c>
-      <c r="AV50" s="14" t="inlineStr">
-        <is>
-          <t>广东省东莞市黄江镇</t>
-        </is>
-      </c>
-      <c r="AW50" s="13" t="inlineStr">
-        <is>
-          <t>https://www.amazon.com/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2UKVTD4STWRQG</t>
-        </is>
-      </c>
-      <c r="AX50" s="13"/>
-      <c r="AY50" s="13"/>
-      <c r="AZ50" s="13"/>
-      <c r="BA50" s="13"/>
-      <c r="BB50" s="13"/>
-      <c r="BC50" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="BD50" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="BE50" s="13"/>
-      <c r="BF50" s="13"/>
-      <c r="BG50" s="13"/>
-      <c r="BH50" s="14"/>
-      <c r="BI50" s="23"/>
-      <c r="BJ50" s="23" t="inlineStr">
-        <is>
-          <t>7.7 pounds</t>
-        </is>
-      </c>
-      <c r="BK50" s="23" t="inlineStr">
-        <is>
-          <t>3.49 kg</t>
-        </is>
-      </c>
-      <c r="BL50" s="23" t="inlineStr">
-        <is>
-          <t>11.8 x 2.9 x 11.8 inches</t>
-        </is>
-      </c>
-      <c r="BM50" s="23" t="inlineStr">
-        <is>
-          <t>29.97 x 7.37 x 29.97 cm</t>
-        </is>
-      </c>
-      <c r="BN50" s="23" t="inlineStr">
-        <is>
-          <t>7.72 pounds</t>
-        </is>
-      </c>
-      <c r="BO50" s="23" t="inlineStr">
-        <is>
-          <t>3.50 kg</t>
-        </is>
-      </c>
-      <c r="BP50" s="23" t="inlineStr">
-        <is>
-          <t>16.9 x 13.7 x 5.3 inches</t>
-        </is>
-      </c>
-      <c r="BQ50" s="23" t="inlineStr">
-        <is>
-          <t>42.93 x 34.80 x 13.46 cm</t>
-        </is>
-      </c>
-      <c r="BR50" s="13" t="inlineStr">
-        <is>
-          <t>大号标准尺寸</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="13">
-        <v>50</v>
-      </c>
-      <c r="B51" s="13"/>
-      <c r="C51" s="14" t="inlineStr">
-        <is>
-          <t>B07RG7X3Q9</t>
-        </is>
-      </c>
-      <c r="D51" s="14"/>
-      <c r="E51" s="14"/>
-      <c r="F51" s="14" t="inlineStr">
-        <is>
-          <t>iRobot</t>
-        </is>
-      </c>
-      <c r="G51" s="14" t="inlineStr">
-        <is>
-          <t>https://www.amazon.com/stores/iRobot%C2%AE/page/A144A34F-3D29-45A4-9DF7-8E77C31F8C7F?lp_asin=B07RG7X3Q9&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
-        </is>
-      </c>
-      <c r="H51" s="14" t="inlineStr">
-        <is>
-          <t>iRobot® Authentic Replacement Parts- Braava Jet® m Series Dry Sweeping Pads, (7-Pack)</t>
-        </is>
-      </c>
-      <c r="I51" s="14"/>
-      <c r="J51" s="14" t="inlineStr">
-        <is>
-          <t>https://www.amazon.com/dp/B07RG7X3Q9?psc=1</t>
-        </is>
-      </c>
-      <c r="K51" s="14" t="inlineStr">
-        <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/717-XciGC4L._AC_US600_.jpg</t>
-        </is>
-      </c>
-      <c r="L51" s="14" t="inlineStr">
-        <is>
-          <t>B07RG7X3Q9</t>
-        </is>
-      </c>
-      <c r="M51" s="14" t="inlineStr">
-        <is>
-          <t>Home &amp; Kitchen:Vacuums &amp; Floor Care:Vacuums:Robotic Vacuums</t>
-        </is>
-      </c>
-      <c r="N51" s="14" t="inlineStr">
-        <is>
-          <t>Home &amp; Kitchen</t>
-        </is>
-      </c>
-      <c r="O51" s="15">
-        <v>51739</v>
-      </c>
-      <c r="P51" s="15">
-        <v>23857</v>
-      </c>
-      <c r="Q51" s="16">
-        <v>0.32</v>
-      </c>
-      <c r="R51" s="17" t="inlineStr">
-        <is>
-          <t>Sweepers &amp; Accessories
-Robotic Vacuums</t>
-        </is>
-      </c>
-      <c r="S51" s="18" t="inlineStr">
-        <is>
-          <t>19
-49</t>
-        </is>
-      </c>
-      <c r="T51" s="15">
-        <v>467</v>
-      </c>
-      <c r="U51" s="16">
-        <v>2.53</v>
-      </c>
-      <c r="V51" s="15">
-        <v>3358</v>
-      </c>
-      <c r="W51" s="15" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
-      <c r="X51" s="15">
-        <v>3196</v>
-      </c>
-      <c r="Y51" s="19">
-        <v>2</v>
-      </c>
-      <c r="Z51" s="20">
-        <v>7.99</v>
-      </c>
-      <c r="AA51" s="4"/>
-      <c r="AB51" s="1"/>
-      <c r="AC51" s="2">
-        <v>6</v>
-      </c>
-      <c r="AD51" s="19">
-        <v>1805</v>
-      </c>
-      <c r="AE51" s="15">
-        <v>7</v>
-      </c>
-      <c r="AF51" s="21">
-        <v>4.7</v>
-      </c>
-      <c r="AG51" s="22">
-        <v>0.015</v>
-      </c>
-      <c r="AH51" s="20">
-        <v>3.91</v>
-      </c>
-      <c r="AI51" s="16">
-        <v>0.31</v>
-      </c>
-      <c r="AJ51"/>
-      <c r="AK51" s="13" t="inlineStr">
-        <is>
-          <t>2019-06-10</t>
-        </is>
-      </c>
-      <c r="AL51" s="19">
-        <v>2638</v>
-      </c>
-      <c r="AM51" s="13" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="AN51" s="13"/>
-      <c r="AO51" s="13"/>
-      <c r="AP51" s="4"/>
-      <c r="AQ51" s="19">
-        <v>10</v>
-      </c>
-      <c r="AR51" s="19">
-        <v>1</v>
-      </c>
-      <c r="AS51" s="14" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-      <c r="AT51" s="13" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="AU51" s="13"/>
-      <c r="AV51" s="14"/>
-      <c r="AW51" s="13"/>
-      <c r="AX51" s="13"/>
-      <c r="AY51" s="13"/>
-      <c r="AZ51" s="13"/>
-      <c r="BA51" s="13"/>
-      <c r="BB51" s="13"/>
-      <c r="BC51" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="BD51" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="BE51" s="13"/>
-      <c r="BF51" s="13"/>
-      <c r="BG51" s="13"/>
-      <c r="BH51" s="14"/>
-      <c r="BI51" s="23"/>
-      <c r="BJ51" s="23" t="inlineStr">
-        <is>
-          <t>0.05 pounds</t>
-        </is>
-      </c>
-      <c r="BK51" s="23" t="inlineStr">
-        <is>
-          <t>22.68 g</t>
-        </is>
-      </c>
-      <c r="BL51" s="23" t="inlineStr">
-        <is>
-          <t>4.2 x 10.6 x 0.3 inches</t>
-        </is>
-      </c>
-      <c r="BM51" s="23" t="inlineStr">
-        <is>
-          <t>10.67 x 26.92 x 0.76 cm</t>
-        </is>
-      </c>
-      <c r="BN51" s="23" t="inlineStr">
-        <is>
-          <t>0.44 pounds</t>
-        </is>
-      </c>
-      <c r="BO51" s="23" t="inlineStr">
-        <is>
-          <t>199.58 g</t>
-        </is>
-      </c>
-      <c r="BP51" s="23" t="inlineStr">
-        <is>
-          <t>11.1 x 4.7 x 2.5 inches</t>
-        </is>
-      </c>
-      <c r="BQ51" s="23" t="inlineStr">
-        <is>
-          <t>28.19 x 11.94 x 6.35 cm</t>
-        </is>
-      </c>
-      <c r="BR51" s="13" t="inlineStr">
         <is>
           <t>大号标准尺寸</t>
         </is>
@@ -20151,70 +19597,55 @@
     <hyperlink ref="M43" r:id="rId315" tooltip="https://www.amazon.com/b?node=3743561"/>
     <hyperlink ref="N43" r:id="rId316"/>
     <hyperlink ref="AW43" r:id="rId317" tooltip="https://www.amazon.com/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2NZXCP1D8DIIH"/>
-    <hyperlink ref="C44" r:id="rId318" tooltip="https://www.amazon.com/dp/B0C7C7PLLG"/>
-    <hyperlink ref="G44" r:id="rId319" tooltip="https://www.amazon.com/stores/eufy/page/B02CB877-324C-4130-B1A3-41E418F2C467?lp_asin=B0C7C7PLLG&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J44" r:id="rId320" tooltip="https://www.amazon.com/dp/B0C7C7PLLG?psc=1"/>
-    <hyperlink ref="K44" r:id="rId321" tooltip="https://images-na.ssl-images-amazon.com/images/I/511jqutQR2L._AC_US600_.jpg"/>
-    <hyperlink ref="L44" r:id="rId322" tooltip="https://www.amazon.com/dp/B0C7C7PLLG"/>
-    <hyperlink ref="M44" r:id="rId323" tooltip="https://www.amazon.com/b?node=3256980011"/>
+    <hyperlink ref="C44" r:id="rId318" tooltip="https://www.amazon.com/dp/B0GZPM94M2"/>
+    <hyperlink ref="G44" r:id="rId319" tooltip="https://www.amazon.com/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Redroad"/>
+    <hyperlink ref="J44" r:id="rId320" tooltip="https://www.amazon.com/dp/B0GZPM94M2?psc=1"/>
+    <hyperlink ref="K44" r:id="rId321" tooltip="https://images-na.ssl-images-amazon.com/images/I/71GaguO8jGL._AC_US600_.jpg"/>
+    <hyperlink ref="L44" r:id="rId322" tooltip="https://www.amazon.com/dp/B0GZPM94M2"/>
+    <hyperlink ref="M44" r:id="rId323" tooltip="https://www.amazon.com/b?node=3743561"/>
     <hyperlink ref="N44" r:id="rId324"/>
-    <hyperlink ref="AW44" r:id="rId325" tooltip="https://www.amazon.com/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1U62USFOR8NN3"/>
-    <hyperlink ref="C45" r:id="rId326" tooltip="https://www.amazon.com/dp/B0GZPM94M2"/>
-    <hyperlink ref="G45" r:id="rId327" tooltip="https://www.amazon.com/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Redroad"/>
-    <hyperlink ref="J45" r:id="rId328" tooltip="https://www.amazon.com/dp/B0GZPM94M2?psc=1"/>
-    <hyperlink ref="K45" r:id="rId329" tooltip="https://images-na.ssl-images-amazon.com/images/I/71GaguO8jGL._AC_US600_.jpg"/>
-    <hyperlink ref="L45" r:id="rId330" tooltip="https://www.amazon.com/dp/B0GZPM94M2"/>
+    <hyperlink ref="AW44" r:id="rId325" tooltip="https://www.amazon.com/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1C6K1RF1VZ7JZ"/>
+    <hyperlink ref="C45" r:id="rId326" tooltip="https://www.amazon.com/dp/B0HBWDF8XN"/>
+    <hyperlink ref="G45" r:id="rId327" tooltip="https://www.amazon.com/stores/UMMUNDRobotVaccuumandMop/page/E436C8FC-A6A3-4981-93C0-1497D6853AF8?lp_asin=B0HBWDF8XN&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J45" r:id="rId328" tooltip="https://www.amazon.com/dp/B0HBWDF8XN?psc=1"/>
+    <hyperlink ref="K45" r:id="rId329" tooltip="https://images-na.ssl-images-amazon.com/images/I/811PjBfyLYL._AC_US600_.jpg"/>
+    <hyperlink ref="L45" r:id="rId330" tooltip="https://www.amazon.com/dp/B0HBWDF8XN"/>
     <hyperlink ref="M45" r:id="rId331" tooltip="https://www.amazon.com/b?node=3743561"/>
     <hyperlink ref="N45" r:id="rId332"/>
-    <hyperlink ref="AW45" r:id="rId333" tooltip="https://www.amazon.com/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1C6K1RF1VZ7JZ"/>
-    <hyperlink ref="C46" r:id="rId334" tooltip="https://www.amazon.com/dp/B0BCF8N3B4"/>
-    <hyperlink ref="G46" r:id="rId335" tooltip="https://www.amazon.com/stores/ECOVACS/page/E74F14EC-79FC-433B-8BB9-DA6190E35D28?lp_asin=B0BCF8N3B4&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J46" r:id="rId336" tooltip="https://www.amazon.com/dp/B0BCF8N3B4?psc=1"/>
-    <hyperlink ref="K46" r:id="rId337" tooltip="https://images-na.ssl-images-amazon.com/images/I/51OKmAG4ODL._AC_US600_.jpg"/>
-    <hyperlink ref="L46" r:id="rId338" tooltip="https://www.amazon.com/dp/B0BCF8N3B4"/>
-    <hyperlink ref="M46" r:id="rId339" tooltip="https://www.amazon.com/b?node=3256980011"/>
+    <hyperlink ref="AW45" r:id="rId333" tooltip="https://www.amazon.com/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3TSG3NHMTCHQR"/>
+    <hyperlink ref="C46" r:id="rId334" tooltip="https://www.amazon.com/dp/B0GWH7M8L9"/>
+    <hyperlink ref="G46" r:id="rId335" tooltip="https://www.amazon.com/stores/BOTLUXE/page/5E044AA6-CC48-4FCC-B008-B011598BBA8B?lp_asin=B0GWH7M8L9&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J46" r:id="rId336" tooltip="https://www.amazon.com/dp/B0GWH7M8L9?psc=1"/>
+    <hyperlink ref="K46" r:id="rId337" tooltip="https://images-na.ssl-images-amazon.com/images/I/71mRKmu7xhL._AC_US600_.jpg"/>
+    <hyperlink ref="L46" r:id="rId338" tooltip="https://www.amazon.com/dp/B0GWH7M8L9"/>
+    <hyperlink ref="M46" r:id="rId339" tooltip="https://www.amazon.com/b?node=3743561"/>
     <hyperlink ref="N46" r:id="rId340"/>
-    <hyperlink ref="C47" r:id="rId341" tooltip="https://www.amazon.com/dp/B0HBWDF8XN"/>
-    <hyperlink ref="G47" r:id="rId342" tooltip="https://www.amazon.com/stores/UMMUNDRobotVaccuumandMop/page/E436C8FC-A6A3-4981-93C0-1497D6853AF8?lp_asin=B0HBWDF8XN&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J47" r:id="rId343" tooltip="https://www.amazon.com/dp/B0HBWDF8XN?psc=1"/>
-    <hyperlink ref="K47" r:id="rId344" tooltip="https://images-na.ssl-images-amazon.com/images/I/811PjBfyLYL._AC_US600_.jpg"/>
-    <hyperlink ref="L47" r:id="rId345" tooltip="https://www.amazon.com/dp/B0HBWDF8XN"/>
-    <hyperlink ref="M47" r:id="rId346" tooltip="https://www.amazon.com/b?node=3743561"/>
-    <hyperlink ref="N47" r:id="rId347"/>
-    <hyperlink ref="AW47" r:id="rId348" tooltip="https://www.amazon.com/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3TSG3NHMTCHQR"/>
-    <hyperlink ref="C48" r:id="rId349" tooltip="https://www.amazon.com/dp/B0GWH7M8L9"/>
-    <hyperlink ref="G48" r:id="rId350" tooltip="https://www.amazon.com/stores/BOTLUXE/page/5E044AA6-CC48-4FCC-B008-B011598BBA8B?lp_asin=B0GWH7M8L9&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J48" r:id="rId351" tooltip="https://www.amazon.com/dp/B0GWH7M8L9?psc=1"/>
-    <hyperlink ref="K48" r:id="rId352" tooltip="https://images-na.ssl-images-amazon.com/images/I/71mRKmu7xhL._AC_US600_.jpg"/>
-    <hyperlink ref="L48" r:id="rId353" tooltip="https://www.amazon.com/dp/B0GWH7M8L9"/>
-    <hyperlink ref="M48" r:id="rId354" tooltip="https://www.amazon.com/b?node=3743561"/>
-    <hyperlink ref="N48" r:id="rId355"/>
-    <hyperlink ref="AW48" r:id="rId356" tooltip="https://www.amazon.com/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2KXKLM92VNJJ5"/>
-    <hyperlink ref="C49" r:id="rId357" tooltip="https://www.amazon.com/dp/B0BVQC5P6W"/>
-    <hyperlink ref="G49" r:id="rId358" tooltip="https://www.amazon.com/stores/Roborock/page/69ADA24D-41D1-454D-9AAC-68D2B6252352?lp_asin=B0BVQC5P6W&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J49" r:id="rId359" tooltip="https://www.amazon.com/dp/B0BVQC5P6W?psc=1"/>
-    <hyperlink ref="K49" r:id="rId360" tooltip="https://images-na.ssl-images-amazon.com/images/I/41954aVFRAL._AC_US600_.jpg"/>
-    <hyperlink ref="L49" r:id="rId361" tooltip="https://www.amazon.com/dp/B0BVQC5P6W"/>
-    <hyperlink ref="M49" r:id="rId362" tooltip="https://www.amazon.com/b?node=3743561"/>
-    <hyperlink ref="N49" r:id="rId363"/>
-    <hyperlink ref="AW49" r:id="rId364" tooltip="https://www.amazon.com/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2NZXCP1D8DIIH"/>
-    <hyperlink ref="C50" r:id="rId365" tooltip="https://www.amazon.com/dp/B0HFCGGZSH"/>
-    <hyperlink ref="G50" r:id="rId366" tooltip="https://www.amazon.com/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=ZC+WAS"/>
-    <hyperlink ref="J50" r:id="rId367" tooltip="https://www.amazon.com/dp/B0HFCGGZSH?psc=1"/>
-    <hyperlink ref="K50" r:id="rId368" tooltip="https://images-na.ssl-images-amazon.com/images/I/81uJWk6uyXL._AC_US600_.jpg"/>
-    <hyperlink ref="L50" r:id="rId369" tooltip="https://www.amazon.com/dp/B0HFCGGZSH"/>
-    <hyperlink ref="M50" r:id="rId370" tooltip="https://www.amazon.com/b?node=3743561"/>
-    <hyperlink ref="N50" r:id="rId371"/>
-    <hyperlink ref="AW50" r:id="rId372" tooltip="https://www.amazon.com/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2UKVTD4STWRQG"/>
-    <hyperlink ref="C51" r:id="rId373" tooltip="https://www.amazon.com/dp/B07RG7X3Q9"/>
-    <hyperlink ref="G51" r:id="rId374" tooltip="https://www.amazon.com/stores/iRobot%C2%AE/page/A144A34F-3D29-45A4-9DF7-8E77C31F8C7F?lp_asin=B07RG7X3Q9&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J51" r:id="rId375" tooltip="https://www.amazon.com/dp/B07RG7X3Q9?psc=1"/>
-    <hyperlink ref="K51" r:id="rId376" tooltip="https://images-na.ssl-images-amazon.com/images/I/717-XciGC4L._AC_US600_.jpg"/>
-    <hyperlink ref="L51" r:id="rId377" tooltip="https://www.amazon.com/dp/B07RG7X3Q9"/>
-    <hyperlink ref="M51" r:id="rId378" tooltip="https://www.amazon.com/b?node=3743561"/>
-    <hyperlink ref="N51" r:id="rId379"/>
+    <hyperlink ref="AW46" r:id="rId341" tooltip="https://www.amazon.com/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2KXKLM92VNJJ5"/>
+    <hyperlink ref="C47" r:id="rId342" tooltip="https://www.amazon.com/dp/B0BVQC5P6W"/>
+    <hyperlink ref="G47" r:id="rId343" tooltip="https://www.amazon.com/stores/Roborock/page/69ADA24D-41D1-454D-9AAC-68D2B6252352?lp_asin=B0BVQC5P6W&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J47" r:id="rId344" tooltip="https://www.amazon.com/dp/B0BVQC5P6W?psc=1"/>
+    <hyperlink ref="K47" r:id="rId345" tooltip="https://images-na.ssl-images-amazon.com/images/I/41954aVFRAL._AC_US600_.jpg"/>
+    <hyperlink ref="L47" r:id="rId346" tooltip="https://www.amazon.com/dp/B0BVQC5P6W"/>
+    <hyperlink ref="M47" r:id="rId347" tooltip="https://www.amazon.com/b?node=3743561"/>
+    <hyperlink ref="N47" r:id="rId348"/>
+    <hyperlink ref="AW47" r:id="rId349" tooltip="https://www.amazon.com/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2NZXCP1D8DIIH"/>
+    <hyperlink ref="C48" r:id="rId350" tooltip="https://www.amazon.com/dp/B0HFCGGZSH"/>
+    <hyperlink ref="G48" r:id="rId351" tooltip="https://www.amazon.com/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=ZC+WAS"/>
+    <hyperlink ref="J48" r:id="rId352" tooltip="https://www.amazon.com/dp/B0HFCGGZSH?psc=1"/>
+    <hyperlink ref="K48" r:id="rId353" tooltip="https://images-na.ssl-images-amazon.com/images/I/81uJWk6uyXL._AC_US600_.jpg"/>
+    <hyperlink ref="L48" r:id="rId354" tooltip="https://www.amazon.com/dp/B0HFCGGZSH"/>
+    <hyperlink ref="M48" r:id="rId355" tooltip="https://www.amazon.com/b?node=3743561"/>
+    <hyperlink ref="N48" r:id="rId356"/>
+    <hyperlink ref="AW48" r:id="rId357" tooltip="https://www.amazon.com/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2UKVTD4STWRQG"/>
+    <hyperlink ref="C49" r:id="rId358" tooltip="https://www.amazon.com/dp/B07RG7X3Q9"/>
+    <hyperlink ref="G49" r:id="rId359" tooltip="https://www.amazon.com/stores/iRobot%C2%AE/page/A144A34F-3D29-45A4-9DF7-8E77C31F8C7F?lp_asin=B07RG7X3Q9&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J49" r:id="rId360" tooltip="https://www.amazon.com/dp/B07RG7X3Q9?psc=1"/>
+    <hyperlink ref="K49" r:id="rId361" tooltip="https://images-na.ssl-images-amazon.com/images/I/717-XciGC4L._AC_US600_.jpg"/>
+    <hyperlink ref="L49" r:id="rId362" tooltip="https://www.amazon.com/dp/B07RG7X3Q9"/>
+    <hyperlink ref="M49" r:id="rId363" tooltip="https://www.amazon.com/b?node=3743561"/>
+    <hyperlink ref="N49" r:id="rId364"/>
   </hyperlinks>
-  <drawing r:id="rId380"/>
+  <drawing r:id="rId365"/>
 </worksheet>
 </file>
 
@@ -20284,7 +19715,7 @@
         <v>429.86097698374374</v>
       </c>
       <c r="G2" s="22">
-        <v>0.2249395834653295</v>
+        <v>0.23453690945810762</v>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20305,7 +19736,7 @@
         <v>305.38104220702667</v>
       </c>
       <c r="G3" s="22">
-        <v>0.19192998017794594</v>
+        <v>0.2001189105528397</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20326,7 +19757,7 @@
         <v>395.6760131129246</v>
       </c>
       <c r="G4" s="22">
-        <v>0.12976657042259895</v>
+        <v>0.13530322190974123</v>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20347,7 +19778,7 @@
         <v>548.0749849306811</v>
       </c>
       <c r="G5" s="22">
-        <v>0.07507942398378031</v>
+        <v>0.07828278061946736</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20357,18 +19788,18 @@
         </is>
       </c>
       <c r="B6" s="15">
-        <v>6262</v>
+        <v>4195</v>
       </c>
       <c r="C6" s="15">
-        <v>2446711</v>
+        <v>2395057</v>
       </c>
       <c r="D6" s="15"/>
       <c r="E6" s="15"/>
       <c r="F6" s="20">
-        <v>390.7235707441712</v>
+        <v>570.931346841478</v>
       </c>
       <c r="G6" s="22">
-        <v>0.056678403012228123</v>
+        <v>0.03958966421924841</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20389,7 +19820,7 @@
         <v>655.476130256086</v>
       </c>
       <c r="G7" s="22">
-        <v>0.028628838825882717</v>
+        <v>0.029850323700949397</v>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20399,18 +19830,18 @@
         </is>
       </c>
       <c r="B8" s="15">
-        <v>8550</v>
+        <v>6096</v>
       </c>
       <c r="C8" s="15">
-        <v>1109854</v>
+        <v>1036259</v>
       </c>
       <c r="D8" s="15"/>
       <c r="E8" s="15"/>
       <c r="F8" s="20">
-        <v>129.80748538011696</v>
+        <v>169.9899934383202</v>
       </c>
       <c r="G8" s="22">
-        <v>0.07738747137568676</v>
+        <v>0.057530057945301145</v>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20431,7 +19862,7 @@
         <v>131.26811805961427</v>
       </c>
       <c r="G9" s="22">
-        <v>0.06194618176552049</v>
+        <v>0.06458919235197523</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20452,7 +19883,7 @@
         <v>146.63934426229508</v>
       </c>
       <c r="G10" s="22">
-        <v>0.039752722138247515</v>
+        <v>0.04144882127555161</v>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20473,7 +19904,7 @@
         <v>99.98992852501624</v>
       </c>
       <c r="G11" s="22">
-        <v>0.055718979390494465</v>
+        <v>0.058096298673109226</v>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20494,7 +19925,7 @@
         <v>99.04236939531057</v>
       </c>
       <c r="G12" s="22">
-        <v>0.044006770272349595</v>
+        <v>0.04588437364338159</v>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20515,7 +19946,7 @@
         <v>239.9897119341564</v>
       </c>
       <c r="G13" s="22">
-        <v>0.004398866793986405</v>
+        <v>0.004586549895245465</v>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20536,7 +19967,7 @@
         <v>239.99078341013825</v>
       </c>
       <c r="G14" s="22">
-        <v>0.0039282061493623455</v>
+        <v>0.004095807931145127</v>
       </c>
     </row>
     <row r="15" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20557,7 +19988,7 @@
         <v>299.9903381642512</v>
       </c>
       <c r="G15" s="22">
-        <v>0.001873591412253469</v>
+        <v>0.0019535305109378833</v>
       </c>
     </row>
     <row r="16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20578,7 +20009,7 @@
         <v>125.98986486486487</v>
       </c>
       <c r="G16" s="22">
-        <v>0.002679145207860033</v>
+        <v>0.0027934542571865385</v>
       </c>
     </row>
     <row r="17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20599,7 +20030,7 @@
         <v>369.9888888888889</v>
       </c>
       <c r="G17" s="22">
-        <v>0.0008146049618493343</v>
+        <v>0.0008493610917121232</v>
       </c>
     </row>
     <row r="18" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20620,7 +20051,7 @@
         <v>109.98076923076923</v>
       </c>
       <c r="G18" s="22">
-        <v>0.00047066064462405983</v>
+        <v>0.0004907419641003378</v>
       </c>
     </row>
   </sheetData>
@@ -20684,18 +20115,18 @@
         </is>
       </c>
       <c r="B2" s="15">
-        <v>38489</v>
+        <v>36422</v>
       </c>
       <c r="C2" s="15">
-        <v>14586579</v>
+        <v>14534925</v>
       </c>
       <c r="D2" s="15"/>
       <c r="E2" s="15"/>
       <c r="F2" s="20">
-        <v>378.9804619501676</v>
+        <v>399.0699302619296</v>
       </c>
       <c r="G2" s="22">
-        <v>0.3483703375179892</v>
+        <v>0.3437269964704328</v>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20716,7 +20147,7 @@
         <v>429.86097698374374</v>
       </c>
       <c r="G3" s="22">
-        <v>0.2249395834653295</v>
+        <v>0.23453690945810762</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20737,7 +20168,7 @@
         <v>469.9900328330206</v>
       </c>
       <c r="G4" s="22">
-        <v>0.0771883457183458</v>
+        <v>0.0804816821124554</v>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20758,7 +20189,7 @@
         <v>303.0368278355174</v>
       </c>
       <c r="G5" s="22">
-        <v>0.040060461790501704</v>
+        <v>0.04176969102130953</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20768,18 +20199,18 @@
         </is>
       </c>
       <c r="B6" s="15">
-        <v>8550</v>
+        <v>6096</v>
       </c>
       <c r="C6" s="15">
-        <v>1109854</v>
+        <v>1036259</v>
       </c>
       <c r="D6" s="15"/>
       <c r="E6" s="15"/>
       <c r="F6" s="20">
-        <v>129.80748538011696</v>
+        <v>169.9899934383202</v>
       </c>
       <c r="G6" s="22">
-        <v>0.07738747137568676</v>
+        <v>0.057530057945301145</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20800,7 +20231,7 @@
         <v>1099.0</v>
       </c>
       <c r="G7" s="22">
-        <v>0.008345175275834291</v>
+        <v>0.008701232517317529</v>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20821,7 +20252,7 @@
         <v>131.26811805961427</v>
       </c>
       <c r="G8" s="22">
-        <v>0.06194618176552049</v>
+        <v>0.06458919235197523</v>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20842,7 +20273,7 @@
         <v>99.98992852501624</v>
       </c>
       <c r="G9" s="22">
-        <v>0.055718979390494465</v>
+        <v>0.058096298673109226</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20863,7 +20294,7 @@
         <v>99.04236939531057</v>
       </c>
       <c r="G10" s="22">
-        <v>0.044006770272349595</v>
+        <v>0.04588437364338159</v>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20884,7 +20315,7 @@
         <v>199.98983050847457</v>
       </c>
       <c r="G11" s="22">
-        <v>0.013350470208086312</v>
+        <v>0.013920084558615353</v>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20905,7 +20336,7 @@
         <v>295.98996655518397</v>
       </c>
       <c r="G12" s="22">
-        <v>0.008118896119765032</v>
+        <v>0.008465298880730828</v>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20926,7 +20357,7 @@
         <v>89.97987616099071</v>
       </c>
       <c r="G13" s="22">
-        <v>0.023388213571318664</v>
+        <v>0.024386100677601403</v>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20947,7 +20378,7 @@
         <v>239.9897119341564</v>
       </c>
       <c r="G14" s="22">
-        <v>0.004398866793986405</v>
+        <v>0.004586549895245465</v>
       </c>
     </row>
     <row r="15" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20968,7 +20399,7 @@
         <v>349.990990990991</v>
       </c>
       <c r="G15" s="22">
-        <v>0.003014038358842537</v>
+        <v>0.003142636039334856</v>
       </c>
     </row>
     <row r="16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20989,7 +20420,7 @@
         <v>239.99078341013825</v>
       </c>
       <c r="G16" s="22">
-        <v>0.0039282061493623455</v>
+        <v>0.004095807931145127</v>
       </c>
     </row>
     <row r="17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21010,7 +20441,7 @@
         <v>299.9903381642512</v>
       </c>
       <c r="G17" s="22">
-        <v>0.001873591412253469</v>
+        <v>0.0019535305109378833</v>
       </c>
     </row>
     <row r="18" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21031,7 +20462,7 @@
         <v>125.98986486486487</v>
       </c>
       <c r="G18" s="22">
-        <v>0.002679145207860033</v>
+        <v>0.0027934542571865385</v>
       </c>
     </row>
     <row r="19" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21052,7 +20483,7 @@
         <v>369.9888888888889</v>
       </c>
       <c r="G19" s="22">
-        <v>0.0008146049618493343</v>
+        <v>0.0008493610917121232</v>
       </c>
     </row>
     <row r="20" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21073,7 +20504,7 @@
         <v>109.98076923076923</v>
       </c>
       <c r="G20" s="22">
-        <v>0.00047066064462405983</v>
+        <v>0.0004907419641003378</v>
       </c>
     </row>
   </sheetData>
